--- a/data/trans_camb/IP16B06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Clase-trans_camb.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 0,0</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 0,0</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">

--- a/data/trans_camb/IP16B06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Clase-trans_camb.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
